--- a/templates/FIM EMBIII - template.xlsx
+++ b/templates/FIM EMBIII - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$E$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$E$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1185,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="50" min="1" max="1"/>
@@ -1193,8 +1193,8 @@
     <col width="5.42578125" customWidth="1" style="50" min="6" max="6"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="50" min="7" max="7"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="50" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="50" min="9" max="14"/>
-    <col width="9.140625" customWidth="1" style="50" min="15" max="16384"/>
+    <col width="9.140625" customWidth="1" style="50" min="9" max="15"/>
+    <col width="9.140625" customWidth="1" style="50" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1322,81 +1322,81 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="28" t="n">
-        <v>167.1715837</v>
+        <v>168.9441309</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>0.0002883127080279824</v>
+        <v>-0.001547058326227146</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>-0.0009170533056662711</v>
+        <v>0.004910425210446823</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="31" t="n">
-        <v>167.1233999</v>
+        <v>169.2059023</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>0.003200413137282698</v>
+        <v>0.004738622060092235</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>0.0009698038351333427</v>
+        <v>0.0002801602825248661</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="31" t="n">
-        <v>166.5902423</v>
+        <v>168.407881</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>-0.002498147813184137</v>
+        <v>0.00206183197723564</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>-0.001486203423446297</v>
+        <v>0.002675085368210928</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="31" t="n">
-        <v>167.0074516</v>
+        <v>168.0613667</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>-0.002798990277400937</v>
+        <v>-0.0001335202961753046</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>9.063037308632005e-05</v>
+        <v>-0.001710874990352274</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>167.4762159</v>
+        <v>168.0838093</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>-0.002073683873764276</v>
+        <v>-0.001265437176820816</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>-0.0005719387689082644</v>
+        <v>0.000347441160196027</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1430,15 +1430,15 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr"/>
       <c r="D24" s="35" t="n">
-        <v>-0.008384325610185095</v>
+        <v>0.007188283329783163</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>-0.01414625293009431</v>
+        <v>0.01040156876119025</v>
       </c>
       <c r="F24" s="36" t="n"/>
     </row>
@@ -1450,10 +1450,10 @@
       </c>
       <c r="C25" s="39" t="inlineStr"/>
       <c r="D25" s="39" t="n">
-        <v>-0.00169934696539864</v>
+        <v>-0.001646988678637995</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>-0.005238640584375398</v>
+        <v>0.009613820770912662</v>
       </c>
       <c r="F25" s="36" t="n"/>
     </row>
@@ -1465,10 +1465,10 @@
       </c>
       <c r="C26" s="39" t="inlineStr"/>
       <c r="D26" s="39" t="n">
-        <v>0.05931215306580406</v>
+        <v>0.04892924494809292</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>0.02702954609003627</v>
+        <v>0.03391362969425371</v>
       </c>
       <c r="F26" s="36" t="n"/>
     </row>
@@ -1480,10 +1480,10 @@
       </c>
       <c r="C27" s="39" t="inlineStr"/>
       <c r="D27" s="39" t="n">
-        <v>0.1369573670557946</v>
+        <v>0.1362955667182078</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>0.08199135899450116</v>
+        <v>0.09321067373329073</v>
       </c>
       <c r="F27" s="36" t="n"/>
     </row>
@@ -1495,185 +1495,192 @@
       </c>
       <c r="C28" s="39" t="inlineStr"/>
       <c r="D28" s="39" t="n">
-        <v>0.241579696591812</v>
+        <v>0.2531605482450612</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.1785026737967914</v>
+        <v>0.2046184695659672</v>
       </c>
       <c r="F28" s="36" t="n"/>
     </row>
-    <row r="29" ht="15.95" customFormat="1" customHeight="1" s="19">
+    <row r="29" ht="15.95" customFormat="1" customHeight="1" s="37">
       <c r="B29" s="38" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="39" t="inlineStr"/>
       <c r="D29" s="39" t="n">
-        <v>0.043302718820317</v>
+        <v>0.1828048783261802</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>0.0215452505886935</v>
-      </c>
-      <c r="F29" s="48" t="n"/>
+        <v>0.1440427330675194</v>
+      </c>
+      <c r="F29" s="36" t="n"/>
     </row>
     <row r="30" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="39" t="inlineStr"/>
       <c r="D30" s="39" t="n">
-        <v>0.215875808493329</v>
+        <v>0.05436502541613186</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>0.2114797129911303</v>
+        <v>0.03589638996532729</v>
       </c>
       <c r="F30" s="48" t="n"/>
     </row>
     <row r="31" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B31" s="38" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="39" t="inlineStr"/>
       <c r="D31" s="39" t="n">
-        <v>-0.05101775882740089</v>
+        <v>0.215875808493329</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>-0.05893224377383777</v>
+        <v>0.2114797129911303</v>
       </c>
       <c r="F31" s="48" t="n"/>
     </row>
     <row r="32" ht="15.95" customFormat="1" customHeight="1" s="19">
-      <c r="A32" s="30" t="n"/>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="39" t="inlineStr"/>
       <c r="D32" s="39" t="n">
-        <v>0.671715837</v>
+        <v>-0.05101775882740089</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>0.544587645381436</v>
+        <v>-0.05893224377383777</v>
       </c>
       <c r="F32" s="48" t="n"/>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
-      <c r="B34" s="23" t="inlineStr">
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="19">
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr"/>
+      <c r="D33" s="39" t="n">
+        <v>0.689441309</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>0.5662867258338404</v>
+      </c>
+      <c r="F33" s="48" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="B35" s="40" t="inlineStr">
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="24" t="n">
-        <v>73310036.03</v>
-      </c>
-      <c r="F35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="B36" s="41" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="24" t="n">
-        <v>71779257.70281747</v>
+        <v>74087354.11</v>
       </c>
       <c r="F36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="B37" s="40" t="n"/>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
+      <c r="E37" s="24" t="n">
+        <v>71995375.0331746</v>
+      </c>
       <c r="F37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
+      <c r="B38" s="40" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
       <c r="F38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">² Cota Inicial em: </t>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C39" s="43" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
       <c r="F39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">² Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>2019-05-16</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
       <c r="F40" s="4" t="n"/>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
+    <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="4" t="n"/>
-      <c r="B41" s="49" t="inlineStr">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
       <c r="F43" s="4" t="n"/>
     </row>
     <row r="44">
@@ -1685,17 +1692,25 @@
       <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="26" t="n"/>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B41:E42"/>
+    <mergeCell ref="B42:E43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="88" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="86"/>
 </worksheet>
 </file>